--- a/docs/Heatpump specs/modbus/Adlar III/HHi/Adlar-III_register_map_merged.xlsx
+++ b/docs/Heatpump specs/modbus/Adlar III/HHi/Adlar-III_register_map_merged.xlsx
@@ -8,13 +8,14 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Register Map (master)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HA Integration" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discrepancies &amp; Notes" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage &amp; Roadmap" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status app 1.9.3" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Register Map (master)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HA Integration" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discrepancies &amp; Notes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage &amp; Roadmap" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Register Map (master)'!$A$1:$O$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Register Map (master)'!$A$1:$O$126</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -123,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -151,6 +152,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -537,6 +556,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Bijgewerkt naar app-versie 1.9.3 (oktober 2026): zie tabblad 'Status app 1.9.3' en de kolom 'Status app 1.9.3' per tabblad. De oorspronkelijke analyse hieronder is ongewijzigd behouden.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr"/>
     </row>
@@ -555,7 +581,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr"/>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Bron — Uitgebreide HA-package 'adlar_warmtepomp.yaml' (2026) en de Homey-app (lib/modbus/adlar3-modbus-registers.ts). Bij tegenspraak is de officiële register map leidend.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -710,7 +740,925 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O126"/>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Officiële register map</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>App 1.9.3</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Capability / functie</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Afwijking / opmerking</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Hardwareverificatie</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>0 = geen thermostaat; 1-3 = met thermostaat (enkele zone / twee zones)</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>Gelezen bij verbinden</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>4-2114 werkt mogelijk niet zonder thermostaat</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>0 = één zone, 1 = twee zones</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>Gelezen bij verbinden</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>Standaardwaarde bij aanzetten via 4-2101 (1 of 3)</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Koudemiddel: 0 = R32, 1 = R290</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Gelezen bij verbinden</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Bepaalt of stille modus niveau 2 is toegestaan</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>Map: niveau 2 alleen voor R290</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>3-9</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Effectieve modus: bit 0 koelen, bit 1 verwarmen, bit 2 tapwater</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Medium-poll (30 s)</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>adlar_dhw_active; gebouwmodel slaat tapwaterperiodes over</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>3-10..31</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Statische limieten per zone en modus</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Slow-poll (5 min)</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>3-14/15 begrenzen 4-2105; 3-30/31 begrenzen 4-2114</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Map-typo x1 bij 3-16 en 3-27</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Schaal 3-16/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>3-38</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Systeemstatus (bitveld)</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Superfast-poll</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>adlar_defrosting, adlar_antifreeze, adlar_sterilization</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Bits 0, 1, 2, 4, 11 bekend (HA)</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Overige bits</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>3-39</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>B0/B1: aanvraag externe warmtebron tijdens vorstbeveiliging / ontdooien (alleen hybride)</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Gelezen, niet gedecodeerd; bittabel in expertdashboard</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>HA-YAML noemt het externe vorstbeveiliging/ontdooien; app volgt de map (gecorrigeerd in 1.9.3)</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>3-63</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Titel: PWM-percentage terugkoppeling; schaal x10, eenheid m³/h</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>x0.1 m³/h, alleen dashboard</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Map spreekt zichzelf tegen; HA leest % x1. App volgt de map (gecorrigeerd in 1.9.3)</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>3-64</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Werkelijk debiet, m³/h, schaal niet opgegeven</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>x0.1 m³/h, getoond in L/min</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>measure_water</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Eenheid/schaal</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>3-66..69</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Stooklijn-setpoints</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Slow-poll (was eenmalig)</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>3-67</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Schaal x1</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>x0.1 (zoals HA), @verify</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>Map x1 tegenover HA x10</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>3-74/75</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Spanning x1 V, stroom x10 A</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Spanning × stroom = vermogen</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>measure_power, measure_voltage, measure_current</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>Geven op sommige firmware 0 (HA); app logt dit eenmalig</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Non-lineariteit stroomsensor</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>3-81</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Vierwegklep: 0 uit, 1 aan</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Gelezen</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>HA: 1 = koelen/ontdooien</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>3-90..95</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>E01-E96, bit voor bit</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Bitveld → E-codes (bijv. E03)</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>adlar_fault, adlar_fault_active, alarm_generic, flowtrigger fault_detected</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>Tot 1.9.0: één code per register</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Omschrijving per code</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>3-96..101</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>P01-P96, bit voor bit (3-101 = P81-P96)</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Bitveld → P-codes</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Idem</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>HA-YAML leest 3-101 als doelmodus; volgens de map onjuist</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>3-102</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Doelmodus: B3-B0 zone 1, B7-B4 zone 2 (0 standby, 1 koelen, 2 verwarmen), B11-B8 tapwater (0 standby, 8 tapwater)</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Gelezen, niet gedecodeerd</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>Bovenste bits (auto-doelmodus) onduidelijk in de map</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>3-103</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Werkelijke modus: zelfde indeling als 3-102</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Gelezen, niet gedecodeerd</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>4-2100</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>1 koelen, 2 verwarmen, 4 auto</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Lezen en schrijven (1/2/4)</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>adlar_mode</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>0 wordt nooit geschreven; aan/uit via 4-2101</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>4-2101</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>0 alles uit, 1 zone 1 aan, 2 zone 2 aan, 3 alles aan</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Lezen; schrijven alleen met instelling 'Aan/uit via zonebesturing (experimenteel)'</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>onoff</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Ja (testgebruikers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>4-2102</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>0 tapwater uit, 1 aan</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Lezen en schrijven</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>adlar_dhw_enabled, flowkaart set_dhw_function</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>4-2103 bit 3</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Geforceerde elektrische verwarming</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Read-modify-write</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>adlar_backup_heater_forced, flowkaart set_backup_heater</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>Ja (overige bits behouden)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>4-2103 bit 4-5</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Stille modus 0/1/2; niveau 2 alleen R290</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Read-modify-write; niveau 2 alleen bij 3-7 = R290 (1.9.3)</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>adlar_silent_mode, flowkaarten set_silent_mode / silent_mode_is</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>4-2103 bit 6</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Desinfectiemodus (schrijfbaar)</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Alleen lezen</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>adlar_disinfection_enabled</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>Bewust niet schrijfbaar gemaakt</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>4-2105</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Tapwater-setpoint x10</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Lezen en schrijven, begrensd door 3-14/15</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>target_temperature.dhw</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>4-2107</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>Zone 1 verwarmings-setpoint x10</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>Lezen en schrijven</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>target_temperature</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>Wordt overschreven door de eigen stooklijn van de regelaar (JAN-module)</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>4-2109</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Zone 1 auto-verwarming, schaal x1 volgens map</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>Schrijven geblokkeerd</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>Vermoedelijk typo (x10)</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>4-2114</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>Kamertemperatuur-setpoint x10</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>Lezen; schrijven via dashboard (16-28 °C of 3-31..30)</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>target_temperature.floor (weergave)</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>Werking zonder thermostaat</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -728,6 +1676,8 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="55" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -804,6 +1754,16 @@
       <c r="O1" s="4" t="inlineStr">
         <is>
           <t>Has Discrepancy?</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>In app 1.9.3?</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>App 1.9.3 — gebruik</t>
         </is>
       </c>
     </row>
@@ -887,6 +1847,16 @@
       <c r="M3" s="5" t="inlineStr"/>
       <c r="N3" s="5" t="inlineStr"/>
       <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q3" s="12" t="inlineStr">
+        <is>
+          <t>Gelezen bij verbinden</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
@@ -926,6 +1896,16 @@
       <c r="M4" s="5" t="inlineStr"/>
       <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q4" s="12" t="inlineStr">
+        <is>
+          <t>Standaard zone-waarde voor aan/uit</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -1129,6 +2109,16 @@
       <c r="M9" s="5" t="inlineStr"/>
       <c r="N9" s="5" t="inlineStr"/>
       <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q9" s="12" t="inlineStr">
+        <is>
+          <t>Bepaalt stille modus niveau 2 (R290)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
@@ -1215,6 +2205,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q11" s="12" t="inlineStr">
+        <is>
+          <t>adlar_dhw_active</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
@@ -1430,6 +2430,16 @@
       <c r="M16" s="5" t="inlineStr"/>
       <c r="N16" s="5" t="inlineStr"/>
       <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q16" s="12" t="inlineStr">
+        <is>
+          <t>Bovengrens 4-2105</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
@@ -1473,6 +2483,16 @@
       <c r="M17" s="5" t="inlineStr"/>
       <c r="N17" s="5" t="inlineStr"/>
       <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q17" s="12" t="inlineStr">
+        <is>
+          <t>Ondergrens 4-2105</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
@@ -2122,6 +3142,16 @@
       <c r="M32" s="5" t="inlineStr"/>
       <c r="N32" s="5" t="inlineStr"/>
       <c r="O32" s="5" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q32" s="12" t="inlineStr">
+        <is>
+          <t>Bovengrens 4-2114</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
@@ -2165,6 +3195,16 @@
       <c r="M33" s="5" t="inlineStr"/>
       <c r="N33" s="5" t="inlineStr"/>
       <c r="O33" s="5" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q33" s="12" t="inlineStr">
+        <is>
+          <t>Ondergrens 4-2114</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
@@ -2451,6 +3491,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q40" s="12" t="inlineStr">
+        <is>
+          <t>adlar_defrosting, adlar_antifreeze, adlar_sterilization</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
@@ -2495,6 +3545,16 @@
       <c r="M41" s="5" t="inlineStr"/>
       <c r="N41" s="5" t="inlineStr"/>
       <c r="O41" s="5" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q41" s="12" t="inlineStr">
+        <is>
+          <t>Gelezen (bittabel dashboard)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n">
@@ -2538,6 +3598,16 @@
       <c r="M42" s="5" t="inlineStr"/>
       <c r="N42" s="5" t="inlineStr"/>
       <c r="O42" s="5" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q42" s="12" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
@@ -2581,6 +3651,16 @@
       <c r="M43" s="5" t="inlineStr"/>
       <c r="N43" s="5" t="inlineStr"/>
       <c r="O43" s="5" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q43" s="12" t="inlineStr">
+        <is>
+          <t>measure_temperature.total_outlet</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -2644,6 +3724,16 @@
         </is>
       </c>
       <c r="O44" s="7" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q44" s="12" t="inlineStr">
+        <is>
+          <t>measure_temperature.inlet</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -2707,6 +3797,16 @@
         </is>
       </c>
       <c r="O45" s="7" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q45" s="12" t="inlineStr">
+        <is>
+          <t>measure_temperature.outlet</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
@@ -2793,6 +3893,16 @@
       <c r="M47" s="5" t="inlineStr"/>
       <c r="N47" s="5" t="inlineStr"/>
       <c r="O47" s="5" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q47" s="12" t="inlineStr">
+        <is>
+          <t>measure_temperature.buffer_tank</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n">
@@ -2840,6 +3950,16 @@
       <c r="M48" s="5" t="inlineStr"/>
       <c r="N48" s="5" t="inlineStr"/>
       <c r="O48" s="5" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q48" s="12" t="inlineStr">
+        <is>
+          <t>measure_temperature.dhw</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
@@ -2883,6 +4003,16 @@
       <c r="M49" s="5" t="inlineStr"/>
       <c r="N49" s="5" t="inlineStr"/>
       <c r="O49" s="5" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q49" s="12" t="inlineStr">
+        <is>
+          <t>measure_temperature.zone2</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n">
@@ -2977,6 +4107,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q51" s="12" t="inlineStr">
+        <is>
+          <t>measure_temperature.outer_coil</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -3036,6 +4176,16 @@
       </c>
       <c r="N52" s="7" t="inlineStr"/>
       <c r="O52" s="7" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q52" s="12" t="inlineStr">
+        <is>
+          <t>measure_temperature.ambient</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
@@ -3122,6 +4272,16 @@
       <c r="M54" s="5" t="inlineStr"/>
       <c r="N54" s="5" t="inlineStr"/>
       <c r="O54" s="5" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q54" s="12" t="inlineStr">
+        <is>
+          <t>measure_temperature.exhaust</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
@@ -3165,6 +4325,16 @@
       <c r="M55" s="5" t="inlineStr"/>
       <c r="N55" s="5" t="inlineStr"/>
       <c r="O55" s="5" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q55" s="12" t="inlineStr">
+        <is>
+          <t>measure_temperature.suction</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n">
@@ -3278,6 +4448,16 @@
       <c r="M58" s="5" t="inlineStr"/>
       <c r="N58" s="5" t="inlineStr"/>
       <c r="O58" s="5" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q58" s="12" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
@@ -3430,6 +4610,16 @@
       <c r="M62" s="5" t="inlineStr"/>
       <c r="N62" s="5" t="inlineStr"/>
       <c r="O62" s="5" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q62" s="12" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
@@ -3489,6 +4679,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q63" s="12" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
@@ -3556,6 +4756,16 @@
         </is>
       </c>
       <c r="O64" s="7" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q64" s="12" t="inlineStr">
+        <is>
+          <t>adlar_pump_pwm</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
@@ -3603,6 +4813,16 @@
       <c r="M65" s="5" t="inlineStr"/>
       <c r="N65" s="5" t="inlineStr"/>
       <c r="O65" s="5" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q65" s="12" t="inlineStr">
+        <is>
+          <t>Dashboard (x0.1 m³/h, @verify)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -3664,6 +4884,16 @@
       <c r="O66" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q66" s="12" t="inlineStr">
+        <is>
+          <t>measure_water</t>
         </is>
       </c>
     </row>
@@ -3744,6 +4974,16 @@
       <c r="M68" s="5" t="inlineStr"/>
       <c r="N68" s="5" t="inlineStr"/>
       <c r="O68" s="5" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q68" s="12" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
@@ -3795,6 +5035,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q69" s="12" t="inlineStr">
+        <is>
+          <t>Dashboard (x0.1, @verify)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n">
@@ -3838,6 +5088,16 @@
       <c r="M70" s="5" t="inlineStr"/>
       <c r="N70" s="5" t="inlineStr"/>
       <c r="O70" s="5" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q70" s="12" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
@@ -3881,6 +5141,16 @@
       <c r="M71" s="5" t="inlineStr"/>
       <c r="N71" s="5" t="inlineStr"/>
       <c r="O71" s="5" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q71" s="12" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="n">
@@ -3928,6 +5198,16 @@
       <c r="M72" s="5" t="inlineStr"/>
       <c r="N72" s="5" t="inlineStr"/>
       <c r="O72" s="5" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q72" s="12" t="inlineStr">
+        <is>
+          <t>adlar_eev_step</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
@@ -3963,6 +5243,16 @@
       <c r="M73" s="5" t="inlineStr"/>
       <c r="N73" s="5" t="inlineStr"/>
       <c r="O73" s="5" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q73" s="12" t="inlineStr">
+        <is>
+          <t>adlar_evi_step</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
@@ -4026,6 +5316,16 @@
       </c>
       <c r="N74" s="7" t="inlineStr"/>
       <c r="O74" s="7" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q74" s="12" t="inlineStr">
+        <is>
+          <t>adlar_fan_speed</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
@@ -4108,6 +5408,16 @@
       <c r="M76" s="5" t="inlineStr"/>
       <c r="N76" s="5" t="inlineStr"/>
       <c r="O76" s="5" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q76" s="12" t="inlineStr">
+        <is>
+          <t>measure_voltage, measure_power</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
@@ -4155,6 +5465,16 @@
       <c r="M77" s="5" t="inlineStr"/>
       <c r="N77" s="5" t="inlineStr"/>
       <c r="O77" s="5" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q77" s="12" t="inlineStr">
+        <is>
+          <t>measure_current, measure_power</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n">
@@ -4202,6 +5522,16 @@
       <c r="M78" s="5" t="inlineStr"/>
       <c r="N78" s="5" t="inlineStr"/>
       <c r="O78" s="5" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q78" s="12" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
@@ -4249,6 +5579,16 @@
       <c r="M79" s="5" t="inlineStr"/>
       <c r="N79" s="5" t="inlineStr"/>
       <c r="O79" s="5" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q79" s="12" t="inlineStr">
+        <is>
+          <t>measure_current.comp_phase</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="n">
@@ -4288,6 +5628,16 @@
       <c r="M80" s="5" t="inlineStr"/>
       <c r="N80" s="5" t="inlineStr"/>
       <c r="O80" s="5" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q80" s="12" t="inlineStr">
+        <is>
+          <t>measure_frequency.comp_target_freq</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
@@ -4351,6 +5701,16 @@
       </c>
       <c r="N81" s="7" t="inlineStr"/>
       <c r="O81" s="7" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q81" s="12" t="inlineStr">
+        <is>
+          <t>measure_frequency.compressor_freq, adlar_compressor_on</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
@@ -4390,6 +5750,16 @@
       <c r="M82" s="5" t="inlineStr"/>
       <c r="N82" s="5" t="inlineStr"/>
       <c r="O82" s="5" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q82" s="12" t="inlineStr">
+        <is>
+          <t>adlar_running</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
@@ -4429,6 +5799,16 @@
       <c r="M83" s="5" t="inlineStr"/>
       <c r="N83" s="5" t="inlineStr"/>
       <c r="O83" s="5" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q83" s="12" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
@@ -4612,6 +5992,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q88" s="12" t="inlineStr">
+        <is>
+          <t>adlar_high_pressure</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
@@ -4659,6 +6049,16 @@
       <c r="M89" s="5" t="inlineStr"/>
       <c r="N89" s="5" t="inlineStr"/>
       <c r="O89" s="5" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q89" s="12" t="inlineStr">
+        <is>
+          <t>adlar_low_pressure</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="n">
@@ -4772,6 +6172,16 @@
       <c r="M92" s="5" t="inlineStr"/>
       <c r="N92" s="5" t="inlineStr"/>
       <c r="O92" s="5" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q92" s="12" t="inlineStr">
+        <is>
+          <t>Bitveld → E-codes (adlar_fault_active)</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n">
@@ -4807,6 +6217,16 @@
       <c r="M93" s="5" t="inlineStr"/>
       <c r="N93" s="5" t="inlineStr"/>
       <c r="O93" s="5" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q93" s="12" t="inlineStr">
+        <is>
+          <t>Bitveld → E-codes (adlar_fault_active)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="n">
@@ -4842,6 +6262,16 @@
       <c r="M94" s="5" t="inlineStr"/>
       <c r="N94" s="5" t="inlineStr"/>
       <c r="O94" s="5" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q94" s="12" t="inlineStr">
+        <is>
+          <t>Bitveld → E-codes (adlar_fault_active)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
@@ -4877,6 +6307,16 @@
       <c r="M95" s="5" t="inlineStr"/>
       <c r="N95" s="5" t="inlineStr"/>
       <c r="O95" s="5" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q95" s="12" t="inlineStr">
+        <is>
+          <t>Bitveld → E-codes (adlar_fault_active)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="n">
@@ -4912,6 +6352,16 @@
       <c r="M96" s="5" t="inlineStr"/>
       <c r="N96" s="5" t="inlineStr"/>
       <c r="O96" s="5" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q96" s="12" t="inlineStr">
+        <is>
+          <t>Bitveld → E-codes (adlar_fault_active)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n">
@@ -4947,6 +6397,16 @@
       <c r="M97" s="5" t="inlineStr"/>
       <c r="N97" s="5" t="inlineStr"/>
       <c r="O97" s="5" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q97" s="12" t="inlineStr">
+        <is>
+          <t>Bitveld → E-codes (adlar_fault_active)</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="n">
@@ -4990,6 +6450,16 @@
       <c r="M98" s="5" t="inlineStr"/>
       <c r="N98" s="5" t="inlineStr"/>
       <c r="O98" s="5" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q98" s="12" t="inlineStr">
+        <is>
+          <t>Bitveld → P-codes (adlar_fault_active)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n">
@@ -5025,6 +6495,16 @@
       <c r="M99" s="5" t="inlineStr"/>
       <c r="N99" s="5" t="inlineStr"/>
       <c r="O99" s="5" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q99" s="12" t="inlineStr">
+        <is>
+          <t>Bitveld → P-codes (adlar_fault_active)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="n">
@@ -5060,6 +6540,16 @@
       <c r="M100" s="5" t="inlineStr"/>
       <c r="N100" s="5" t="inlineStr"/>
       <c r="O100" s="5" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q100" s="12" t="inlineStr">
+        <is>
+          <t>Bitveld → P-codes (adlar_fault_active)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
@@ -5095,6 +6585,16 @@
       <c r="M101" s="5" t="inlineStr"/>
       <c r="N101" s="5" t="inlineStr"/>
       <c r="O101" s="5" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q101" s="12" t="inlineStr">
+        <is>
+          <t>Bitveld → P-codes (adlar_fault_active)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="n">
@@ -5130,6 +6630,16 @@
       <c r="M102" s="5" t="inlineStr"/>
       <c r="N102" s="5" t="inlineStr"/>
       <c r="O102" s="5" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q102" s="12" t="inlineStr">
+        <is>
+          <t>Bitveld → P-codes (adlar_fault_active)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n">
@@ -5165,6 +6675,16 @@
       <c r="M103" s="5" t="inlineStr"/>
       <c r="N103" s="5" t="inlineStr"/>
       <c r="O103" s="5" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q103" s="12" t="inlineStr">
+        <is>
+          <t>Bitveld → P-codes (adlar_fault_active)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="n">
@@ -5228,6 +6748,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q104" s="12" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="n">
@@ -5285,6 +6815,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q105" s="12" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="n">
@@ -5554,6 +7094,16 @@
         </is>
       </c>
       <c r="O112" s="7" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q112" s="12" t="inlineStr">
+        <is>
+          <t>adlar_mode</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="n">
@@ -5596,6 +7146,16 @@
       <c r="M113" s="8" t="inlineStr"/>
       <c r="N113" s="8" t="inlineStr"/>
       <c r="O113" s="8" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q113" s="12" t="inlineStr">
+        <is>
+          <t>onoff (schrijven experimenteel)</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="8" t="n">
@@ -5636,6 +7196,16 @@
       <c r="M114" s="8" t="inlineStr"/>
       <c r="N114" s="8" t="inlineStr"/>
       <c r="O114" s="8" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q114" s="12" t="inlineStr">
+        <is>
+          <t>adlar_dhw_enabled</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="7" t="n">
@@ -5710,6 +7280,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q115" s="12" t="inlineStr">
+        <is>
+          <t>adlar_backup_heater_forced (b3), adlar_silent_mode (b4-5), adlar_disinfection_enabled (b6)</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="n">
@@ -5793,6 +7373,16 @@
       <c r="M117" s="8" t="inlineStr"/>
       <c r="N117" s="8" t="inlineStr"/>
       <c r="O117" s="8" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q117" s="12" t="inlineStr">
+        <is>
+          <t>target_temperature.dhw</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="8" t="n">
@@ -5836,6 +7426,16 @@
       <c r="M118" s="8" t="inlineStr"/>
       <c r="N118" s="8" t="inlineStr"/>
       <c r="O118" s="8" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q118" s="12" t="inlineStr">
+        <is>
+          <t>target_temperature.cooling</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="7" t="n">
@@ -5897,6 +7497,16 @@
         </is>
       </c>
       <c r="O119" s="7" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q119" s="12" t="inlineStr">
+        <is>
+          <t>target_temperature</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="8" t="n">
@@ -5991,6 +7601,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q121" s="12" t="inlineStr">
+        <is>
+          <t>Schrijven geblokkeerd</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="8" t="n">
@@ -6206,6 +7826,16 @@
       <c r="M126" s="8" t="inlineStr"/>
       <c r="N126" s="8" t="inlineStr"/>
       <c r="O126" s="8" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q126" s="12" t="inlineStr">
+        <is>
+          <t>target_temperature.floor (weergave)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:O126"/>
@@ -6213,13 +7843,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6558,375 +8188,201 @@
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="80" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Register / Item</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Observation</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Explanation / Action</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>Spec typo?</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Reg 16</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>Scale=x1, unit=°C</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>Vermoedelijk x10 (Z1 auto cooling upper limit). Andere upper/lower limits zijn x10. Verifiëren met fysieke meting.</t>
-        </is>
-      </c>
-      <c r="E2" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Spec typo?</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Reg 27</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Scale=x1, unit=°C</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Vermoedelijk x10 (Z2 auto cooling lower limit). Verifiëren.</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Spec typo?</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Reg 67</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Scale=x1, unit=°C</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Vermoedelijk x10 (Z1 climate curve heating set temp). Verifiëren.</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Spec typo?</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Reg 2109</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Scale=x1, unit=°C</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Vermoedelijk x10 (Z1 auto heating temp setting). Belangrijk: dit is een writable register. Verifiëren VÓÓR schrijven.</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Spec gap</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Reg 64</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Scale=NaN, unit=m³/h</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>YAML gebruikt scale=0.1 (komt uit Reg 63 dat x10 is). Spec is incompleet — datasheet/fabrikant raadplegen.</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Spec gap</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Reg 61</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Scale=NaN, unit=Bar</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>YAML gebruikt scale=0.1. Aannemelijk maar niet bevestigd in spec.</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Spec gap</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Reg 86</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Scale=NaN, unit=kPa (high pressure)</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Geen scale opgegeven. Bij gebruik eerst kalibratie nodig.</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Bit-encoding</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Reg 38</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>System status bitmask</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>YAML decoded 5 van mogelijk 16 bits. Volledige bitdefinitie staat niet in spec — alleen via reverse engineering.</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Bit-encoding</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Reg 2103</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Additional function A</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Silent mode in bits 4-5. Andere bits onbekend — voorzichtigheid bij schrijven (huidige YAML preserveert via 'cleared').</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Naming</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Reg 48 vs 49</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Beide heten 'T3'</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Reg 48=Solar water heating T3, Reg 49=Outdoor unit coil T3. Verschillende sensoren met dezelfde labelnaam in spec.</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Encoding</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Reg 9 (Effective mode)</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Bitmask: bit0=cooling, bit1=heating, bit2=DHW</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Read-only configuratie-info — handig voor capability discovery in HA.</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>Info</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Encoding</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Reg 102/103</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Current/Actual operation mode</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Spec geeft niet de enum-waarden. Loggen tijdens gebruik om mapping vast te stellen.</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>select (uitgebr. YAML)</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Warmtepomp zone besturing</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Read/write op Reg 2101</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>0 alles uit / 1 zone 1 / 2 zone 2 / 3 alles aan</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>switch (uitgebr. YAML)</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>WP Tapwater</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Read/write op Reg 2102</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>0 uit / 1 aan</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>switch (uitgebr. YAML)</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>WP Geforceerde elektrische bijverwarming</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>Read-modify-write Reg 2103 bit 3</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Overige bits behouden</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>number (uitgebr. YAML)</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>WP Tapwater setpoint</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Write Reg 2105 (x10)</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>30-60 °C</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>number (uitgebr. YAML)</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>WP Ruimtetemperatuur setpoint</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>Write Reg 2114 (x10)</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>16-28 °C; mogelijk niet zonder thermostaat</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>binary_sensor (uitgebr. YAML)</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>WP Tapwatermodus actief</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Reg 9 bit 2</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Effectieve modus</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>binary_sensor (uitgebr. YAML)</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>WP Desinfectie ingeschakeld</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Reg 2103 bit 6</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>Alleen lezen</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>binary_sensor (uitgebr. YAML)</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>WP E-storing / P-beveiliging actief</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Reg 90/91, 96/97 &gt; 0</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>Bitvelden; alleen eerste 32 codes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>template_sensor (uitgebr. YAML)</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>WP Verwarmings- / Koelvermogen</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>1.163 × flow × ΔT</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>0 bij ontdooien, stilstand of flow &lt; 0.3 m³/h</t>
         </is>
       </c>
     </row>
@@ -6941,7 +8397,637 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Register / Item</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Explanation / Action</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Status app 1.9.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Spec typo?</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Reg 16</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Scale=x1, unit=°C</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Vermoedelijk x10 (Z1 auto cooling upper limit). Andere upper/lower limits zijn x10. Verifiëren met fysieke meting.</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>Open; app gebruikt x10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Spec typo?</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Reg 27</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Scale=x1, unit=°C</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Vermoedelijk x10 (Z2 auto cooling lower limit). Verifiëren.</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>Open; app gebruikt x10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Spec typo?</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Reg 67</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Scale=x1, unit=°C</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Vermoedelijk x10 (Z1 climate curve heating set temp). Verifiëren.</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>Open; app gebruikt x10 zoals HA (@verify), alleen lezen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Spec typo?</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Reg 2109</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Scale=x1, unit=°C</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Vermoedelijk x10 (Z1 auto heating temp setting). Belangrijk: dit is een writable register. Verifiëren VÓÓR schrijven.</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>Schrijven in de app geblokkeerd tot verificatie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Spec gap</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Reg 64</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Scale=NaN, unit=m³/h</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>YAML gebruikt scale=0.1 (komt uit Reg 63 dat x10 is). Spec is incompleet — datasheet/fabrikant raadplegen.</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>App: x0.1 m³/h, getoond in L/min (@verify).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Spec gap</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Reg 61</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Scale=NaN, unit=Bar</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>YAML gebruikt scale=0.1. Aannemelijk maar niet bevestigd in spec.</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>App: x0.1 bar, alleen dashboard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Spec gap</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Reg 86</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Scale=NaN, unit=kPa (high pressure)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Geen scale opgegeven. Bij gebruik eerst kalibratie nodig.</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>App: x1 kPa (adlar_high_pressure, @verify).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Bit-encoding</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Reg 38</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>System status bitmask</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>YAML decoded 5 van mogelijk 16 bits. Volledige bitdefinitie staat niet in spec — alleen via reverse engineering.</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>Ongewijzigd: 5 bits bekend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Bit-encoding</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Reg 2103</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Additional function A</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Silent mode in bits 4-5. Andere bits onbekend — voorzichtigheid bij schrijven (huidige YAML preserveert via 'cleared').</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>Opgelost: officiële map documenteert bit 3, 4-5 en 6; overige bits gereserveerd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Naming</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Reg 48 vs 49</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Beide heten 'T3'</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Reg 48=Solar water heating T3, Reg 49=Outdoor unit coil T3. Verschillende sensoren met dezelfde labelnaam in spec.</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Encoding</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Reg 9 (Effective mode)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Bitmask: bit0=cooling, bit1=heating, bit2=DHW</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Read-only configuratie-info — handig voor capability discovery in HA.</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>In gebruik: adlar_dhw_active (bit 2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Encoding</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Reg 102/103</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Current/Actual operation mode</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Spec geeft niet de enum-waarden. Loggen tijdens gebruik om mapping vast te stellen.</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>Opgelost: officiële map documenteert de indeling per zone en tapwater.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>HA vs map</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Reg 39</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>HA: 'externe vorstbeveiliging / extern ontdooien'</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>Map: aanvraag externe warmtebron tijdens vorstbeveiliging / ontdooien (alleen hybride). App volgt de map.</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>Gecorrigeerd in 1.9.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>Spec tegenstrijdig</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Reg 63</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Titel 'percentage', maar schaal x10 en eenheid m³/h; HA leest % x1</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>App volgt de map (x0.1 m³/h) met @verify. Alleen dashboard.</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>Gecorrigeerd in 1.9.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>HA vs map</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Reg 101</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>HA-YAML leest de doelmodus uit Reg 101</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Map: Reg 101 = P81-P96, doelmodus staat in Reg 102. App volgt de map.</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>Opgelost</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>Beperking</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>Reg 2103 bits 4-5</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Stille modus niveau 2 alleen voor R290-warmtepompen</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>App weigert niveau 2 tenzij Reg 7 = R290.</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>Ingevoerd in 1.9.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Nieuw</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>Reg 2101</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>Zonebesturing 0 alles uit … 3 alles aan</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Gebruikt als aan/uit; schrijven alleen met experimentele instelling.</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>Hardwaretest door testgebruikers</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Encoding</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>Reg 90-101</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Map: 'bit by bit operation'</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>App decodeert per bit (E03, P17) sinds 1.9.0.</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>Opgelost</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6949,6 +9035,7 @@
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -6977,6 +9064,11 @@
           <t>Priority</t>
         </is>
       </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Status app 1.9.3</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -7004,6 +9096,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>Zie tabblad 'Status app 1.9.3'</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -7031,6 +9128,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>In app: measure_temperature.dhw</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -7058,6 +9160,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>In app: adlar_dhw_enabled + flowkaart</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -7085,6 +9192,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>In app: target_temperature.dhw (begrensd door 3-14/15)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -7112,6 +9224,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>Gelezen; alleen dashboard</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -7139,6 +9256,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>In app: adlar_high_pressure</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -7166,6 +9288,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>In app: adlar_low_pressure</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -7193,6 +9320,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>In app: measure_temperature.exhaust</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -7220,6 +9352,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>In app: measure_temperature.suction</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -7247,6 +9384,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>In app: measure_temperature.outer_coil</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -7274,6 +9416,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>Gelezen; indeling gedocumenteerd, niet gedecodeerd</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -7301,6 +9448,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>In app: bitveld → E-codes, alarm, flowtrigger</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -7328,6 +9480,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>In app: bitveld → P-codes</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -7355,6 +9512,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>In app: adlar_eev_step</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -7382,6 +9544,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>In app: measure_voltage/current/power, comp_phase; 3-76 alleen dashboard</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -7409,6 +9576,11 @@
           <t>Conditional</t>
         </is>
       </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>Reg 47 → measure_temperature.zone2; 2110-2113 alleen dashboard</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -7434,6 +9606,11 @@
       <c r="E18" s="7" t="inlineStr">
         <is>
           <t>Low</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>In app: eenmalig gelezen; 3-2, 3-7 en 3-9 in gebruik</t>
         </is>
       </c>
     </row>
